--- a/products/store_b/out/04_Monthly_Budget_Planner.xlsx
+++ b/products/store_b/out/04_Monthly_Budget_Planner.xlsx
@@ -1088,11 +1088,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="98372910"/>
-        <c:axId val="1457688"/>
+        <c:axId val="34842467"/>
+        <c:axId val="72062129"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="98372910"/>
+        <c:axId val="34842467"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1124,7 +1124,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1457688"/>
+        <c:crossAx val="72062129"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1132,7 +1132,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1457688"/>
+        <c:axId val="72062129"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1174,7 +1174,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98372910"/>
+        <c:crossAx val="34842467"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1603,11 +1603,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="81158075"/>
-        <c:axId val="94138934"/>
+        <c:axId val="4324170"/>
+        <c:axId val="25419353"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="81158075"/>
+        <c:axId val="4324170"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1639,7 +1639,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94138934"/>
+        <c:crossAx val="25419353"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1647,7 +1647,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94138934"/>
+        <c:axId val="25419353"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1689,7 +1689,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81158075"/>
+        <c:crossAx val="4324170"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
